--- a/output/roomself_excel/8593.xlsx
+++ b/output/roomself_excel/8593.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>226417</v>
+        <v>155806</v>
       </c>
       <c r="D2" t="n">
-        <v>4312</v>
+        <v>3392</v>
       </c>
       <c r="E2" t="n">
-        <v>1347</v>
+        <v>385</v>
       </c>
       <c r="F2" t="n">
-        <v>304</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>159840</v>
+        <v>335306</v>
       </c>
       <c r="D3" t="n">
-        <v>3528</v>
+        <v>5920</v>
       </c>
       <c r="E3" t="n">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F3" t="n">
-        <v>362</v>
+        <v>691</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45440</v>
+        <v>15846</v>
       </c>
       <c r="D4" t="n">
-        <v>1932</v>
+        <v>1012</v>
       </c>
       <c r="E4" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15846</v>
+        <v>31542</v>
       </c>
       <c r="D5" t="n">
-        <v>1012</v>
+        <v>1616</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31542</v>
+        <v>16520</v>
       </c>
       <c r="D6" t="n">
-        <v>1616</v>
+        <v>1032</v>
       </c>
       <c r="E6" t="n">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>153715</v>
+        <v>60250</v>
       </c>
       <c r="D7" t="n">
-        <v>3152</v>
+        <v>1964</v>
       </c>
       <c r="E7" t="n">
-        <v>721</v>
+        <v>285</v>
       </c>
       <c r="F7" t="n">
-        <v>393</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>304874</v>
+        <v>16732</v>
       </c>
       <c r="D8" t="n">
-        <v>6302</v>
+        <v>1108</v>
       </c>
       <c r="E8" t="n">
-        <v>1074</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>34190</v>
+        <v>40247</v>
       </c>
       <c r="D9" t="n">
-        <v>1764</v>
+        <v>1632</v>
       </c>
       <c r="E9" t="n">
-        <v>463</v>
+        <v>255</v>
       </c>
       <c r="F9" t="n">
-        <v>384</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>101068</v>
+        <v>140175</v>
       </c>
       <c r="D10" t="n">
-        <v>2852</v>
+        <v>4760</v>
       </c>
       <c r="E10" t="n">
-        <v>574</v>
+        <v>390</v>
       </c>
       <c r="F10" t="n">
-        <v>283</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>155806</v>
+        <v>45440</v>
       </c>
       <c r="D11" t="n">
-        <v>3392</v>
+        <v>1932</v>
       </c>
       <c r="E11" t="n">
-        <v>764</v>
+        <v>368</v>
       </c>
       <c r="F11" t="n">
-        <v>290</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>222271</v>
+        <v>34190</v>
       </c>
       <c r="D12" t="n">
-        <v>4767</v>
+        <v>1764</v>
       </c>
       <c r="E12" t="n">
-        <v>903</v>
+        <v>384</v>
       </c>
       <c r="F12" t="n">
-        <v>755</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40247</v>
+        <v>332850</v>
       </c>
       <c r="D13" t="n">
-        <v>1632</v>
+        <v>7092</v>
       </c>
       <c r="E13" t="n">
-        <v>578</v>
+        <v>795</v>
       </c>
       <c r="F13" t="n">
-        <v>276</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>161910</v>
+        <v>43776</v>
       </c>
       <c r="D14" t="n">
-        <v>3572</v>
+        <v>1680</v>
       </c>
       <c r="E14" t="n">
-        <v>902</v>
+        <v>261</v>
       </c>
       <c r="F14" t="n">
-        <v>357</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>335306</v>
+        <v>45784</v>
       </c>
       <c r="D15" t="n">
-        <v>5920</v>
+        <v>1720</v>
       </c>
       <c r="E15" t="n">
-        <v>1161</v>
+        <v>250</v>
       </c>
       <c r="F15" t="n">
-        <v>691</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16520</v>
+        <v>62084</v>
       </c>
       <c r="D16" t="n">
-        <v>1032</v>
+        <v>2160</v>
       </c>
       <c r="E16" t="n">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>54576</v>
+        <v>226417</v>
       </c>
       <c r="D17" t="n">
-        <v>2092</v>
+        <v>4312</v>
       </c>
       <c r="E17" t="n">
-        <v>412</v>
+        <v>653</v>
       </c>
       <c r="F17" t="n">
-        <v>177</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67239</v>
+        <v>159840</v>
       </c>
       <c r="D18" t="n">
-        <v>2080</v>
+        <v>3528</v>
       </c>
       <c r="E18" t="n">
-        <v>290</v>
+        <v>646</v>
       </c>
       <c r="F18" t="n">
-        <v>112</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>60250</v>
+        <v>153715</v>
       </c>
       <c r="D19" t="n">
-        <v>1964</v>
+        <v>3152</v>
       </c>
       <c r="E19" t="n">
-        <v>285</v>
+        <v>471</v>
       </c>
       <c r="F19" t="n">
-        <v>276</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>140175</v>
+        <v>304874</v>
       </c>
       <c r="D20" t="n">
-        <v>4760</v>
+        <v>6302</v>
       </c>
       <c r="E20" t="n">
-        <v>404</v>
+        <v>704</v>
       </c>
       <c r="F20" t="n">
-        <v>347</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18740</v>
+        <v>101068</v>
       </c>
       <c r="D21" t="n">
-        <v>1180</v>
+        <v>2852</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16732</v>
+        <v>222271</v>
       </c>
       <c r="D22" t="n">
-        <v>1108</v>
+        <v>4767</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>903</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>564</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>332850</v>
+        <v>161910</v>
       </c>
       <c r="D23" t="n">
-        <v>7092</v>
+        <v>3572</v>
       </c>
       <c r="E23" t="n">
-        <v>1347</v>
+        <v>777</v>
       </c>
       <c r="F23" t="n">
-        <v>1043</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24">
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>43776</v>
+        <v>54576</v>
       </c>
       <c r="D24" t="n">
-        <v>1680</v>
+        <v>2092</v>
       </c>
       <c r="E24" t="n">
-        <v>656</v>
+        <v>412</v>
       </c>
       <c r="F24" t="n">
-        <v>261</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50454</v>
+        <v>67239</v>
       </c>
       <c r="D25" t="n">
-        <v>2656</v>
+        <v>2080</v>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>45784</v>
+        <v>18740</v>
       </c>
       <c r="D26" t="n">
-        <v>1720</v>
+        <v>1180</v>
       </c>
       <c r="E26" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62084</v>
+        <v>50454</v>
       </c>
       <c r="D27" t="n">
-        <v>2160</v>
+        <v>2656</v>
       </c>
       <c r="E27" t="n">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F27" t="n">
-        <v>218</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8593.xlsx
+++ b/output/roomself_excel/8593.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,37 @@
       <c r="D2" t="n">
         <v>3392</v>
       </c>
-      <c r="E2" t="n">
-        <v>385</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>256</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +587,45 @@
       <c r="D3" t="n">
         <v>5920</v>
       </c>
-      <c r="E3" t="n">
-        <v>905</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>691</v>
-      </c>
+        <v>954</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>803</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>245</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +642,21 @@
       <c r="D4" t="n">
         <v>1012</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +673,21 @@
       <c r="D5" t="n">
         <v>1616</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +704,21 @@
       <c r="D6" t="n">
         <v>1032</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +735,37 @@
       <c r="D7" t="n">
         <v>1964</v>
       </c>
-      <c r="E7" t="n">
-        <v>285</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>276</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>241</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +782,21 @@
       <c r="D8" t="n">
         <v>1108</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +813,37 @@
       <c r="D9" t="n">
         <v>1632</v>
       </c>
-      <c r="E9" t="n">
-        <v>255</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>202</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="G9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>220</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +860,37 @@
       <c r="D10" t="n">
         <v>4760</v>
       </c>
-      <c r="E10" t="n">
-        <v>390</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
+        <v>49</v>
+      </c>
+      <c r="G10" t="n">
         <v>34</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>307</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +907,37 @@
       <c r="D11" t="n">
         <v>1932</v>
       </c>
-      <c r="E11" t="n">
-        <v>368</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>166</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="G11" t="n">
+        <v>38</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>128</v>
+      </c>
+      <c r="J11" t="n">
+        <v>38</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +954,60 @@
       <c r="D12" t="n">
         <v>1764</v>
       </c>
-      <c r="E12" t="n">
-        <v>384</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>144</v>
+        <v>31</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>222</v>
+      </c>
+      <c r="P12" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>106</v>
+      </c>
+      <c r="S12" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +1025,53 @@
       <c r="D13" t="n">
         <v>7092</v>
       </c>
-      <c r="E13" t="n">
-        <v>795</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>603</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="G13" t="n">
+        <v>35</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>157</v>
+      </c>
+      <c r="M13" t="n">
+        <v>35</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>362</v>
+      </c>
+      <c r="P13" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1088,37 @@
       <c r="D14" t="n">
         <v>1680</v>
       </c>
-      <c r="E14" t="n">
-        <v>261</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>225</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G14" t="n">
+        <v>33</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>228</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1135,37 @@
       <c r="D15" t="n">
         <v>1720</v>
       </c>
-      <c r="E15" t="n">
-        <v>250</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>227</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G15" t="n">
+        <v>33</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>194</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1182,37 @@
       <c r="D16" t="n">
         <v>2160</v>
       </c>
-      <c r="E16" t="n">
-        <v>400</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>218</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="G16" t="n">
+        <v>26</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>166</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1229,45 @@
       <c r="D17" t="n">
         <v>4312</v>
       </c>
-      <c r="E17" t="n">
-        <v>653</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>266</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="G17" t="n">
+        <v>38</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>222</v>
+      </c>
+      <c r="J17" t="n">
+        <v>37</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>228</v>
+      </c>
+      <c r="M17" t="n">
+        <v>38</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1284,37 @@
       <c r="D18" t="n">
         <v>3528</v>
       </c>
-      <c r="E18" t="n">
-        <v>646</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>362</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="G18" t="n">
+        <v>38</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>570</v>
+      </c>
+      <c r="J18" t="n">
+        <v>38</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1331,37 @@
       <c r="D19" t="n">
         <v>3152</v>
       </c>
-      <c r="E19" t="n">
-        <v>471</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>370</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="G19" t="n">
+        <v>38</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>332</v>
+      </c>
+      <c r="J19" t="n">
+        <v>38</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1378,45 @@
       <c r="D20" t="n">
         <v>6302</v>
       </c>
-      <c r="E20" t="n">
-        <v>704</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>386</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>477</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>212</v>
+      </c>
+      <c r="M20" t="n">
+        <v>38</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1433,37 @@
       <c r="D21" t="n">
         <v>2852</v>
       </c>
-      <c r="E21" t="n">
-        <v>249</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>249</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G21" t="n">
+        <v>34</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>182</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1480,45 @@
       <c r="D22" t="n">
         <v>4767</v>
       </c>
-      <c r="E22" t="n">
-        <v>903</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>564</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>166</v>
+      </c>
+      <c r="J22" t="n">
+        <v>32</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>142</v>
+      </c>
+      <c r="M22" t="n">
+        <v>33</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1535,37 @@
       <c r="D23" t="n">
         <v>3572</v>
       </c>
-      <c r="E23" t="n">
-        <v>777</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>357</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="G23" t="n">
+        <v>34</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>585</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1582,37 @@
       <c r="D24" t="n">
         <v>2092</v>
       </c>
-      <c r="E24" t="n">
-        <v>412</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>177</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="G24" t="n">
+        <v>33</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>379</v>
+      </c>
+      <c r="J24" t="n">
+        <v>33</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1629,29 @@
       <c r="D25" t="n">
         <v>2080</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>77</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>35</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1668,21 @@
       <c r="D26" t="n">
         <v>1180</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1699,29 @@
       <c r="D27" t="n">
         <v>2656</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>50</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>33</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/8593.xlsx
+++ b/output/roomself_excel/8593.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,86 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
         </is>
       </c>
     </row>
@@ -571,6 +651,46 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>159</v>
+      </c>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>118</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -626,6 +746,58 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>400</v>
+      </c>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>461</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>86</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -657,6 +829,22 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -688,6 +876,22 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -719,6 +923,22 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -766,6 +986,34 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>113</v>
+      </c>
+      <c r="W7" t="n">
+        <v>35</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -797,6 +1045,22 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -844,6 +1108,46 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>64</v>
+      </c>
+      <c r="W9" t="n">
+        <v>35</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>84</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -891,6 +1195,58 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>49</v>
+      </c>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>81</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -938,6 +1294,22 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1009,6 +1381,22 @@
       <c r="S12" t="n">
         <v>38</v>
       </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1072,6 +1460,58 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>112</v>
+      </c>
+      <c r="W13" t="n">
+        <v>35</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>39</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1119,6 +1559,22 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1166,6 +1622,22 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1213,6 +1685,34 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>82</v>
+      </c>
+      <c r="W16" t="n">
+        <v>26</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1268,6 +1768,34 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>182</v>
+      </c>
+      <c r="W17" t="n">
+        <v>38</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1315,6 +1843,34 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>176</v>
+      </c>
+      <c r="W18" t="n">
+        <v>38</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1362,6 +1918,34 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>176</v>
+      </c>
+      <c r="W19" t="n">
+        <v>38</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1417,6 +2001,46 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>174</v>
+      </c>
+      <c r="W20" t="n">
+        <v>38</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>82</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1464,6 +2088,70 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>114</v>
+      </c>
+      <c r="W21" t="n">
+        <v>34</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>33</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1519,6 +2207,34 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>117</v>
+      </c>
+      <c r="W22" t="n">
+        <v>35</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1566,6 +2282,46 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>232</v>
+      </c>
+      <c r="W23" t="n">
+        <v>34</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>235</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1613,6 +2369,22 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1652,6 +2424,34 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>63</v>
+      </c>
+      <c r="W25" t="n">
+        <v>35</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1683,6 +2483,22 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1722,6 +2538,22 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
